--- a/Result/28-06-25/NASDAQstock_28-06-25period252RS90.xlsx
+++ b/Result/28-06-25/NASDAQstock_28-06-25period252RS90.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kelvinyue/Desktop/Coding project/StockAnalysis/Result/28-06-25/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A87019A-E9F5-8E42-AC0C-4A245318DBA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEE80EF3-A5F0-9D4A-931E-166D95918E19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Result/28-06-25/NASDAQstock_28-06-25period252RS90.xlsx
+++ b/Result/28-06-25/NASDAQstock_28-06-25period252RS90.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kelvinyue/Desktop/Coding project/StockAnalysis/Result/28-06-25/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEE80EF3-A5F0-9D4A-931E-166D95918E19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1E17DE3-9A61-1342-8B42-367F712D5527}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="140" yWindow="660" windowWidth="28660" windowHeight="15960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -904,6 +904,13 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="9"/>
+      <name val="新細明體"/>
+      <family val="3"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="新細明體"/>
@@ -915,13 +922,6 @@
       <name val="新細明體"/>
       <charset val="136"/>
     </font>
-    <font>
-      <sz val="9"/>
-      <name val="新細明體"/>
-      <family val="3"/>
-      <charset val="136"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -929,6 +929,12 @@
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -946,12 +952,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFA500"/>
         <bgColor rgb="FFFFA500"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -998,12 +998,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -1438,7 +1438,7 @@
       </c>
     </row>
     <row r="2" spans="1:42">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="2" t="s">
         <v>42</v>
       </c>
       <c r="B2">
@@ -1540,7 +1540,7 @@
       <c r="AI2" t="s">
         <v>43</v>
       </c>
-      <c r="AJ2" s="2" t="s">
+      <c r="AJ2" s="3" t="s">
         <v>44</v>
       </c>
       <c r="AK2" t="s">
@@ -1563,7 +1563,7 @@
       </c>
     </row>
     <row r="3" spans="1:42">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="2" t="s">
         <v>47</v>
       </c>
       <c r="B3">
@@ -1665,7 +1665,7 @@
       <c r="AI3" t="s">
         <v>48</v>
       </c>
-      <c r="AJ3" s="3" t="s">
+      <c r="AJ3" s="4" t="s">
         <v>49</v>
       </c>
       <c r="AK3" t="s">
@@ -1688,7 +1688,7 @@
       </c>
     </row>
     <row r="4" spans="1:42">
-      <c r="A4" s="8" t="s">
+      <c r="A4" s="2" t="s">
         <v>51</v>
       </c>
       <c r="B4">
@@ -1790,7 +1790,7 @@
       <c r="AI4" t="s">
         <v>52</v>
       </c>
-      <c r="AJ4" s="2" t="s">
+      <c r="AJ4" s="3" t="s">
         <v>53</v>
       </c>
       <c r="AK4" t="s">
@@ -1813,7 +1813,7 @@
       </c>
     </row>
     <row r="5" spans="1:42">
-      <c r="A5" s="9" t="s">
+      <c r="A5" s="5" t="s">
         <v>55</v>
       </c>
       <c r="B5">
@@ -1873,7 +1873,7 @@
       <c r="U5">
         <v>16.111111111111111</v>
       </c>
-      <c r="V5" s="5" t="b">
+      <c r="V5" s="6" t="b">
         <v>1</v>
       </c>
       <c r="W5" t="b">
@@ -1915,7 +1915,7 @@
       <c r="AI5" t="s">
         <v>56</v>
       </c>
-      <c r="AJ5" s="3" t="s">
+      <c r="AJ5" s="4" t="s">
         <v>49</v>
       </c>
       <c r="AK5" t="s">
@@ -1938,7 +1938,7 @@
       </c>
     </row>
     <row r="6" spans="1:42">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="7" t="s">
         <v>58</v>
       </c>
       <c r="B6">
@@ -2040,7 +2040,7 @@
       <c r="AI6" t="s">
         <v>59</v>
       </c>
-      <c r="AJ6" s="3" t="s">
+      <c r="AJ6" s="4" t="s">
         <v>49</v>
       </c>
       <c r="AK6" t="s">
@@ -2063,7 +2063,7 @@
       </c>
     </row>
     <row r="7" spans="1:42">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="2" t="s">
         <v>61</v>
       </c>
       <c r="B7">
@@ -2165,7 +2165,7 @@
       <c r="AI7" t="s">
         <v>62</v>
       </c>
-      <c r="AJ7" s="3" t="s">
+      <c r="AJ7" s="4" t="s">
         <v>49</v>
       </c>
       <c r="AK7" t="s">
@@ -2188,7 +2188,7 @@
       </c>
     </row>
     <row r="8" spans="1:42" ht="13" customHeight="1">
-      <c r="A8" s="4" t="s">
+      <c r="A8" s="7" t="s">
         <v>65</v>
       </c>
       <c r="B8">
@@ -2290,7 +2290,7 @@
       <c r="AI8" t="s">
         <v>66</v>
       </c>
-      <c r="AJ8" s="3" t="s">
+      <c r="AJ8" s="4" t="s">
         <v>67</v>
       </c>
       <c r="AK8" t="s">
@@ -2313,7 +2313,7 @@
       </c>
     </row>
     <row r="9" spans="1:42">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="2" t="s">
         <v>69</v>
       </c>
       <c r="B9">
@@ -2415,7 +2415,7 @@
       <c r="AI9" t="s">
         <v>52</v>
       </c>
-      <c r="AJ9" s="2" t="s">
+      <c r="AJ9" s="3" t="s">
         <v>53</v>
       </c>
       <c r="AK9" t="s">
@@ -2438,7 +2438,7 @@
       </c>
     </row>
     <row r="10" spans="1:42">
-      <c r="A10" s="8" t="s">
+      <c r="A10" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B10">
@@ -2537,7 +2537,7 @@
       <c r="AI10" t="s">
         <v>73</v>
       </c>
-      <c r="AJ10" s="3" t="s">
+      <c r="AJ10" s="4" t="s">
         <v>67</v>
       </c>
       <c r="AK10" t="s">
@@ -2662,7 +2662,7 @@
       <c r="AI11" t="s">
         <v>56</v>
       </c>
-      <c r="AJ11" s="2" t="s">
+      <c r="AJ11" s="3" t="s">
         <v>77</v>
       </c>
       <c r="AK11" t="s">
@@ -2787,7 +2787,7 @@
       <c r="AI12" t="s">
         <v>81</v>
       </c>
-      <c r="AJ12" s="3" t="s">
+      <c r="AJ12" s="4" t="s">
         <v>67</v>
       </c>
       <c r="AK12" t="s">
@@ -2912,7 +2912,7 @@
       <c r="AI13" t="s">
         <v>84</v>
       </c>
-      <c r="AJ13" s="2" t="s">
+      <c r="AJ13" s="3" t="s">
         <v>85</v>
       </c>
       <c r="AK13" t="s">
@@ -2935,7 +2935,7 @@
       </c>
     </row>
     <row r="14" spans="1:42">
-      <c r="A14" s="4" t="s">
+      <c r="A14" s="7" t="s">
         <v>87</v>
       </c>
       <c r="B14">
@@ -3037,7 +3037,7 @@
       <c r="AI14" t="s">
         <v>88</v>
       </c>
-      <c r="AJ14" s="2" t="s">
+      <c r="AJ14" s="3" t="s">
         <v>89</v>
       </c>
       <c r="AK14" t="s">
@@ -3162,7 +3162,7 @@
       <c r="AI15" t="s">
         <v>93</v>
       </c>
-      <c r="AJ15" s="3" t="s">
+      <c r="AJ15" s="4" t="s">
         <v>67</v>
       </c>
       <c r="AK15" t="s">
@@ -3185,7 +3185,7 @@
       </c>
     </row>
     <row r="16" spans="1:42">
-      <c r="A16" s="4" t="s">
+      <c r="A16" s="7" t="s">
         <v>95</v>
       </c>
       <c r="B16">
@@ -3287,7 +3287,7 @@
       <c r="AI16" t="s">
         <v>96</v>
       </c>
-      <c r="AJ16" s="3" t="s">
+      <c r="AJ16" s="4" t="s">
         <v>67</v>
       </c>
       <c r="AK16" t="s">
@@ -3310,7 +3310,7 @@
       </c>
     </row>
     <row r="17" spans="1:42">
-      <c r="A17" s="8" t="s">
+      <c r="A17" s="2" t="s">
         <v>97</v>
       </c>
       <c r="B17">
@@ -3412,7 +3412,7 @@
       <c r="AI17" t="s">
         <v>48</v>
       </c>
-      <c r="AJ17" s="3" t="s">
+      <c r="AJ17" s="4" t="s">
         <v>67</v>
       </c>
       <c r="AK17" t="s">
@@ -3435,7 +3435,7 @@
       </c>
     </row>
     <row r="18" spans="1:42">
-      <c r="A18" s="8" t="s">
+      <c r="A18" s="2" t="s">
         <v>98</v>
       </c>
       <c r="B18">
@@ -3537,7 +3537,7 @@
       <c r="AI18" t="s">
         <v>66</v>
       </c>
-      <c r="AJ18" s="3" t="s">
+      <c r="AJ18" s="4" t="s">
         <v>67</v>
       </c>
       <c r="AK18" t="s">
@@ -3662,7 +3662,7 @@
       <c r="AI19" t="s">
         <v>100</v>
       </c>
-      <c r="AJ19" s="3" t="s">
+      <c r="AJ19" s="4" t="s">
         <v>101</v>
       </c>
       <c r="AK19" t="s">
@@ -3685,7 +3685,7 @@
       </c>
     </row>
     <row r="20" spans="1:42">
-      <c r="A20" s="8" t="s">
+      <c r="A20" s="2" t="s">
         <v>104</v>
       </c>
       <c r="B20">
@@ -3787,7 +3787,7 @@
       <c r="AI20" t="s">
         <v>52</v>
       </c>
-      <c r="AJ20" s="3" t="s">
+      <c r="AJ20" s="4" t="s">
         <v>49</v>
       </c>
       <c r="AK20" t="s">
@@ -3810,7 +3810,7 @@
       </c>
     </row>
     <row r="21" spans="1:42">
-      <c r="A21" s="4" t="s">
+      <c r="A21" s="7" t="s">
         <v>106</v>
       </c>
       <c r="B21">
@@ -3912,7 +3912,7 @@
       <c r="AI21" t="s">
         <v>84</v>
       </c>
-      <c r="AJ21" s="3" t="s">
+      <c r="AJ21" s="4" t="s">
         <v>67</v>
       </c>
       <c r="AK21" t="s">
@@ -3935,7 +3935,7 @@
       </c>
     </row>
     <row r="22" spans="1:42">
-      <c r="A22" s="8" t="s">
+      <c r="A22" s="2" t="s">
         <v>107</v>
       </c>
       <c r="B22">
@@ -4037,7 +4037,7 @@
       <c r="AI22" t="s">
         <v>43</v>
       </c>
-      <c r="AJ22" s="2" t="s">
+      <c r="AJ22" s="3" t="s">
         <v>53</v>
       </c>
       <c r="AK22" t="s">
@@ -4060,7 +4060,7 @@
       </c>
     </row>
     <row r="23" spans="1:42">
-      <c r="A23" s="8" t="s">
+      <c r="A23" s="2" t="s">
         <v>109</v>
       </c>
       <c r="B23">
@@ -4162,7 +4162,7 @@
       <c r="AI23" t="s">
         <v>52</v>
       </c>
-      <c r="AJ23" s="2" t="s">
+      <c r="AJ23" s="3" t="s">
         <v>53</v>
       </c>
       <c r="AK23" t="s">
@@ -4185,7 +4185,7 @@
       </c>
     </row>
     <row r="24" spans="1:42">
-      <c r="A24" s="4" t="s">
+      <c r="A24" s="7" t="s">
         <v>111</v>
       </c>
       <c r="B24">
@@ -4245,7 +4245,7 @@
       <c r="U24">
         <v>0</v>
       </c>
-      <c r="V24" s="5" t="b">
+      <c r="V24" s="6" t="b">
         <v>1</v>
       </c>
       <c r="W24" t="b">
@@ -4287,7 +4287,7 @@
       <c r="AI24" t="s">
         <v>112</v>
       </c>
-      <c r="AJ24" s="2" t="s">
+      <c r="AJ24" s="3" t="s">
         <v>89</v>
       </c>
       <c r="AK24" t="s">
@@ -4310,7 +4310,7 @@
       </c>
     </row>
     <row r="25" spans="1:42">
-      <c r="A25" s="8" t="s">
+      <c r="A25" s="2" t="s">
         <v>113</v>
       </c>
       <c r="B25">
@@ -4412,7 +4412,7 @@
       <c r="AI25" t="s">
         <v>114</v>
       </c>
-      <c r="AJ25" s="2" t="s">
+      <c r="AJ25" s="3" t="s">
         <v>53</v>
       </c>
       <c r="AK25" t="s">
@@ -4537,7 +4537,7 @@
       <c r="AI26" t="s">
         <v>116</v>
       </c>
-      <c r="AJ26" s="2" t="s">
+      <c r="AJ26" s="3" t="s">
         <v>53</v>
       </c>
       <c r="AK26" t="s">
@@ -4656,7 +4656,7 @@
       <c r="AI27" t="s">
         <v>81</v>
       </c>
-      <c r="AJ27" s="3" t="s">
+      <c r="AJ27" s="4" t="s">
         <v>49</v>
       </c>
       <c r="AK27" t="s">
@@ -4679,7 +4679,7 @@
       </c>
     </row>
     <row r="28" spans="1:42">
-      <c r="A28" s="8" t="s">
+      <c r="A28" s="2" t="s">
         <v>120</v>
       </c>
       <c r="B28">
@@ -4781,7 +4781,7 @@
       <c r="AI28" t="s">
         <v>43</v>
       </c>
-      <c r="AJ28" s="2" t="s">
+      <c r="AJ28" s="3" t="s">
         <v>77</v>
       </c>
       <c r="AK28" t="s">
@@ -4906,7 +4906,7 @@
       <c r="AI29" t="s">
         <v>123</v>
       </c>
-      <c r="AJ29" s="3" t="s">
+      <c r="AJ29" s="4" t="s">
         <v>49</v>
       </c>
       <c r="AK29" t="s">
@@ -4929,7 +4929,7 @@
       </c>
     </row>
     <row r="30" spans="1:42">
-      <c r="A30" s="8" t="s">
+      <c r="A30" s="2" t="s">
         <v>125</v>
       </c>
       <c r="B30">
@@ -4986,7 +4986,7 @@
       <c r="S30">
         <v>1.1200000000000001</v>
       </c>
-      <c r="T30" s="6" t="s">
+      <c r="T30" s="8" t="s">
         <v>19</v>
       </c>
       <c r="U30">
@@ -5034,7 +5034,7 @@
       <c r="AI30" t="s">
         <v>126</v>
       </c>
-      <c r="AJ30" s="3" t="s">
+      <c r="AJ30" s="4" t="s">
         <v>67</v>
       </c>
       <c r="AK30" t="s">
@@ -5057,7 +5057,7 @@
       </c>
     </row>
     <row r="31" spans="1:42">
-      <c r="A31" s="8" t="s">
+      <c r="A31" s="2" t="s">
         <v>128</v>
       </c>
       <c r="B31">
@@ -5090,7 +5090,7 @@
       <c r="K31">
         <v>1.66</v>
       </c>
-      <c r="L31" s="6">
+      <c r="L31" s="8">
         <v>-1.091990857474098</v>
       </c>
       <c r="M31">
@@ -5117,7 +5117,7 @@
       <c r="U31">
         <v>12.22222222222222</v>
       </c>
-      <c r="V31" s="5" t="b">
+      <c r="V31" s="6" t="b">
         <v>1</v>
       </c>
       <c r="W31" t="b">
@@ -5159,7 +5159,7 @@
       <c r="AI31" t="s">
         <v>116</v>
       </c>
-      <c r="AJ31" s="2" t="s">
+      <c r="AJ31" s="3" t="s">
         <v>85</v>
       </c>
       <c r="AK31" t="s">
@@ -5182,7 +5182,7 @@
       </c>
     </row>
     <row r="32" spans="1:42">
-      <c r="A32" s="8" t="s">
+      <c r="A32" s="2" t="s">
         <v>130</v>
       </c>
       <c r="B32">
@@ -5284,7 +5284,7 @@
       <c r="AI32" t="s">
         <v>131</v>
       </c>
-      <c r="AJ32" s="3" t="s">
+      <c r="AJ32" s="4" t="s">
         <v>101</v>
       </c>
       <c r="AK32" t="s">
@@ -5409,7 +5409,7 @@
       <c r="AI33" t="s">
         <v>93</v>
       </c>
-      <c r="AJ33" s="2" t="s">
+      <c r="AJ33" s="3" t="s">
         <v>53</v>
       </c>
       <c r="AK33" t="s">
@@ -5432,7 +5432,7 @@
       </c>
     </row>
     <row r="34" spans="1:42">
-      <c r="A34" s="8" t="s">
+      <c r="A34" s="2" t="s">
         <v>137</v>
       </c>
       <c r="B34">
@@ -5534,7 +5534,7 @@
       <c r="AI34" t="s">
         <v>138</v>
       </c>
-      <c r="AJ34" s="2" t="s">
+      <c r="AJ34" s="3" t="s">
         <v>44</v>
       </c>
       <c r="AK34" t="s">
@@ -5659,7 +5659,7 @@
       <c r="AI35" t="s">
         <v>114</v>
       </c>
-      <c r="AJ35" s="2" t="s">
+      <c r="AJ35" s="3" t="s">
         <v>53</v>
       </c>
       <c r="AK35" t="s">
@@ -5682,7 +5682,7 @@
       </c>
     </row>
     <row r="36" spans="1:42">
-      <c r="A36" s="4" t="s">
+      <c r="A36" s="7" t="s">
         <v>140</v>
       </c>
       <c r="B36">
@@ -5742,7 +5742,7 @@
       <c r="U36">
         <v>0</v>
       </c>
-      <c r="V36" s="5" t="b">
+      <c r="V36" s="6" t="b">
         <v>1</v>
       </c>
       <c r="W36" t="b">
@@ -5784,7 +5784,7 @@
       <c r="AI36" t="s">
         <v>43</v>
       </c>
-      <c r="AJ36" s="3" t="s">
+      <c r="AJ36" s="4" t="s">
         <v>49</v>
       </c>
       <c r="AK36" t="s">
@@ -5909,7 +5909,7 @@
       <c r="AI37" t="s">
         <v>59</v>
       </c>
-      <c r="AJ37" s="3" t="s">
+      <c r="AJ37" s="4" t="s">
         <v>101</v>
       </c>
       <c r="AK37" t="s">
@@ -5932,7 +5932,7 @@
       </c>
     </row>
     <row r="38" spans="1:42">
-      <c r="A38" s="8" t="s">
+      <c r="A38" s="2" t="s">
         <v>145</v>
       </c>
       <c r="B38">
@@ -6034,7 +6034,7 @@
       <c r="AI38" t="s">
         <v>93</v>
       </c>
-      <c r="AJ38" s="2" t="s">
+      <c r="AJ38" s="3" t="s">
         <v>53</v>
       </c>
       <c r="AK38" t="s">
@@ -6057,7 +6057,7 @@
       </c>
     </row>
     <row r="39" spans="1:42">
-      <c r="A39" s="4" t="s">
+      <c r="A39" s="7" t="s">
         <v>147</v>
       </c>
       <c r="B39">
@@ -6117,7 +6117,7 @@
       <c r="U39">
         <v>4.4444444444444438</v>
       </c>
-      <c r="V39" s="5" t="b">
+      <c r="V39" s="6" t="b">
         <v>1</v>
       </c>
       <c r="W39" t="b">
@@ -6153,7 +6153,7 @@
       <c r="AI39" t="s">
         <v>148</v>
       </c>
-      <c r="AJ39" s="3" t="s">
+      <c r="AJ39" s="4" t="s">
         <v>101</v>
       </c>
       <c r="AK39" t="s">
@@ -6176,7 +6176,7 @@
       </c>
     </row>
     <row r="40" spans="1:42">
-      <c r="A40" s="8" t="s">
+      <c r="A40" s="2" t="s">
         <v>149</v>
       </c>
       <c r="B40">
@@ -6236,7 +6236,7 @@
       <c r="U40">
         <v>6.666666666666667</v>
       </c>
-      <c r="V40" s="5" t="b">
+      <c r="V40" s="6" t="b">
         <v>1</v>
       </c>
       <c r="W40" t="b">
@@ -6272,7 +6272,7 @@
       <c r="AI40" t="s">
         <v>48</v>
       </c>
-      <c r="AJ40" s="3" t="s">
+      <c r="AJ40" s="4" t="s">
         <v>101</v>
       </c>
       <c r="AK40" t="s">
@@ -6295,7 +6295,7 @@
       </c>
     </row>
     <row r="41" spans="1:42">
-      <c r="A41" s="8" t="s">
+      <c r="A41" s="2" t="s">
         <v>151</v>
       </c>
       <c r="B41">
@@ -6397,7 +6397,7 @@
       <c r="AI41" t="s">
         <v>59</v>
       </c>
-      <c r="AJ41" s="2" t="s">
+      <c r="AJ41" s="3" t="s">
         <v>44</v>
       </c>
       <c r="AK41" t="s">
@@ -6420,7 +6420,7 @@
       </c>
     </row>
     <row r="42" spans="1:42">
-      <c r="A42" s="9" t="s">
+      <c r="A42" s="5" t="s">
         <v>154</v>
       </c>
       <c r="B42">
@@ -6453,7 +6453,7 @@
       <c r="K42">
         <v>1.58</v>
       </c>
-      <c r="L42" s="6">
+      <c r="L42" s="8">
         <v>-1.1296029849994049</v>
       </c>
       <c r="M42">
@@ -6480,7 +6480,7 @@
       <c r="U42">
         <v>2.7777777777777781</v>
       </c>
-      <c r="V42" s="5" t="b">
+      <c r="V42" s="6" t="b">
         <v>1</v>
       </c>
       <c r="W42" t="b">
@@ -6522,7 +6522,7 @@
       <c r="AI42" t="s">
         <v>155</v>
       </c>
-      <c r="AJ42" s="2" t="s">
+      <c r="AJ42" s="3" t="s">
         <v>156</v>
       </c>
       <c r="AK42" t="s">
@@ -6605,7 +6605,7 @@
       <c r="U43">
         <v>0</v>
       </c>
-      <c r="V43" s="5" t="b">
+      <c r="V43" s="6" t="b">
         <v>1</v>
       </c>
       <c r="W43" t="b">
@@ -6647,7 +6647,7 @@
       <c r="AI43" t="s">
         <v>114</v>
       </c>
-      <c r="AJ43" s="3" t="s">
+      <c r="AJ43" s="4" t="s">
         <v>67</v>
       </c>
       <c r="AK43" t="s">
@@ -6670,7 +6670,7 @@
       </c>
     </row>
     <row r="44" spans="1:42">
-      <c r="A44" s="8" t="s">
+      <c r="A44" s="2" t="s">
         <v>159</v>
       </c>
       <c r="B44">
@@ -6772,7 +6772,7 @@
       <c r="AI44" t="s">
         <v>138</v>
       </c>
-      <c r="AJ44" s="3" t="s">
+      <c r="AJ44" s="4" t="s">
         <v>101</v>
       </c>
       <c r="AK44" t="s">
@@ -6855,7 +6855,7 @@
       <c r="U45">
         <v>0</v>
       </c>
-      <c r="V45" s="5" t="b">
+      <c r="V45" s="6" t="b">
         <v>1</v>
       </c>
       <c r="W45" t="b">
@@ -6897,7 +6897,7 @@
       <c r="AI45" t="s">
         <v>84</v>
       </c>
-      <c r="AJ45" s="3" t="s">
+      <c r="AJ45" s="4" t="s">
         <v>67</v>
       </c>
       <c r="AK45" t="s">
@@ -6920,7 +6920,7 @@
       </c>
     </row>
     <row r="46" spans="1:42">
-      <c r="A46" s="8" t="s">
+      <c r="A46" s="2" t="s">
         <v>161</v>
       </c>
       <c r="B46">
@@ -6953,7 +6953,7 @@
       <c r="K46">
         <v>1.82</v>
       </c>
-      <c r="L46" s="6">
+      <c r="L46" s="8">
         <v>-1.016766602423482</v>
       </c>
       <c r="M46">
@@ -6980,7 +6980,7 @@
       <c r="U46">
         <v>6.1111111111111107</v>
       </c>
-      <c r="V46" s="5" t="b">
+      <c r="V46" s="6" t="b">
         <v>1</v>
       </c>
       <c r="W46" t="b">
@@ -7022,7 +7022,7 @@
       <c r="AI46" t="s">
         <v>131</v>
       </c>
-      <c r="AJ46" s="3" t="s">
+      <c r="AJ46" s="4" t="s">
         <v>67</v>
       </c>
       <c r="AK46" t="s">
@@ -7045,7 +7045,7 @@
       </c>
     </row>
     <row r="47" spans="1:42">
-      <c r="A47" s="8" t="s">
+      <c r="A47" s="2" t="s">
         <v>162</v>
       </c>
       <c r="B47">
@@ -7147,7 +7147,7 @@
       <c r="AI47" t="s">
         <v>48</v>
       </c>
-      <c r="AJ47" s="2" t="s">
+      <c r="AJ47" s="3" t="s">
         <v>44</v>
       </c>
       <c r="AK47" t="s">
@@ -7230,7 +7230,7 @@
       <c r="U48">
         <v>3.333333333333333</v>
       </c>
-      <c r="V48" s="5" t="b">
+      <c r="V48" s="6" t="b">
         <v>1</v>
       </c>
       <c r="W48" t="b">
@@ -7272,7 +7272,7 @@
       <c r="AI48" t="s">
         <v>88</v>
       </c>
-      <c r="AJ48" s="2" t="s">
+      <c r="AJ48" s="3" t="s">
         <v>53</v>
       </c>
       <c r="AK48" t="s">
@@ -7295,7 +7295,7 @@
       </c>
     </row>
     <row r="49" spans="1:42">
-      <c r="A49" s="7" t="s">
+      <c r="A49" s="9" t="s">
         <v>166</v>
       </c>
       <c r="B49">
@@ -7400,7 +7400,7 @@
       <c r="AI49" t="s">
         <v>72</v>
       </c>
-      <c r="AJ49" s="3" t="s">
+      <c r="AJ49" s="4" t="s">
         <v>67</v>
       </c>
       <c r="AK49" t="s">
@@ -7480,7 +7480,7 @@
       <c r="S50">
         <v>1.17</v>
       </c>
-      <c r="T50" s="6" t="s">
+      <c r="T50" s="8" t="s">
         <v>19</v>
       </c>
       <c r="U50">
@@ -7525,7 +7525,7 @@
       <c r="AI50" t="s">
         <v>43</v>
       </c>
-      <c r="AJ50" s="3" t="s">
+      <c r="AJ50" s="4" t="s">
         <v>67</v>
       </c>
       <c r="AK50" t="s">
@@ -7650,7 +7650,7 @@
       <c r="AI51" t="s">
         <v>48</v>
       </c>
-      <c r="AJ51" s="2" t="s">
+      <c r="AJ51" s="3" t="s">
         <v>53</v>
       </c>
       <c r="AK51" t="s">
@@ -7775,7 +7775,7 @@
       <c r="AI52" t="s">
         <v>93</v>
       </c>
-      <c r="AJ52" s="3" t="s">
+      <c r="AJ52" s="4" t="s">
         <v>67</v>
       </c>
       <c r="AK52" t="s">
@@ -7798,7 +7798,7 @@
       </c>
     </row>
     <row r="53" spans="1:42">
-      <c r="A53" s="4" t="s">
+      <c r="A53" s="7" t="s">
         <v>173</v>
       </c>
       <c r="B53">
@@ -7825,13 +7825,13 @@
       <c r="I53">
         <v>0.18</v>
       </c>
-      <c r="J53" s="6">
+      <c r="J53" s="8">
         <v>-1.0327737676615909</v>
       </c>
       <c r="K53">
         <v>0.55000000000000004</v>
       </c>
-      <c r="L53" s="6">
+      <c r="L53" s="8">
         <v>-1.613859126887742</v>
       </c>
       <c r="M53">
@@ -7858,7 +7858,7 @@
       <c r="U53">
         <v>2.7777777777777781</v>
       </c>
-      <c r="V53" s="5" t="b">
+      <c r="V53" s="6" t="b">
         <v>1</v>
       </c>
       <c r="W53" t="b">
@@ -7900,7 +7900,7 @@
       <c r="AI53" t="s">
         <v>93</v>
       </c>
-      <c r="AJ53" s="2" t="s">
+      <c r="AJ53" s="3" t="s">
         <v>53</v>
       </c>
       <c r="AK53" t="s">
@@ -8025,7 +8025,7 @@
       <c r="AI54" t="s">
         <v>175</v>
       </c>
-      <c r="AJ54" s="3" t="s">
+      <c r="AJ54" s="4" t="s">
         <v>67</v>
       </c>
       <c r="AK54" t="s">
@@ -8048,7 +8048,7 @@
       </c>
     </row>
     <row r="55" spans="1:42">
-      <c r="A55" s="4" t="s">
+      <c r="A55" s="7" t="s">
         <v>176</v>
       </c>
       <c r="B55">
@@ -8108,7 +8108,7 @@
       <c r="U55">
         <v>1.1111111111111109</v>
       </c>
-      <c r="V55" s="5" t="b">
+      <c r="V55" s="6" t="b">
         <v>1</v>
       </c>
       <c r="W55" t="b">
@@ -8150,7 +8150,7 @@
       <c r="AI55" t="s">
         <v>48</v>
       </c>
-      <c r="AJ55" s="2" t="s">
+      <c r="AJ55" s="3" t="s">
         <v>89</v>
       </c>
       <c r="AK55" t="s">
@@ -8275,7 +8275,7 @@
       <c r="AI56" t="s">
         <v>43</v>
       </c>
-      <c r="AJ56" s="3" t="s">
+      <c r="AJ56" s="4" t="s">
         <v>101</v>
       </c>
       <c r="AK56" t="s">
@@ -8400,7 +8400,7 @@
       <c r="AI57" t="s">
         <v>180</v>
       </c>
-      <c r="AJ57" s="2" t="s">
+      <c r="AJ57" s="3" t="s">
         <v>156</v>
       </c>
       <c r="AK57" t="s">
@@ -8525,7 +8525,7 @@
       <c r="AI58" t="s">
         <v>175</v>
       </c>
-      <c r="AJ58" s="2" t="s">
+      <c r="AJ58" s="3" t="s">
         <v>53</v>
       </c>
       <c r="AK58" t="s">
@@ -8650,7 +8650,7 @@
       <c r="AI59" t="s">
         <v>175</v>
       </c>
-      <c r="AJ59" s="3" t="s">
+      <c r="AJ59" s="4" t="s">
         <v>49</v>
       </c>
       <c r="AK59" t="s">
@@ -8673,7 +8673,7 @@
       </c>
     </row>
     <row r="60" spans="1:42">
-      <c r="A60" s="4" t="s">
+      <c r="A60" s="7" t="s">
         <v>186</v>
       </c>
       <c r="B60">
@@ -8775,7 +8775,7 @@
       <c r="AI60" t="s">
         <v>59</v>
       </c>
-      <c r="AJ60" s="2" t="s">
+      <c r="AJ60" s="3" t="s">
         <v>89</v>
       </c>
       <c r="AK60" t="s">
@@ -8798,7 +8798,7 @@
       </c>
     </row>
     <row r="61" spans="1:42">
-      <c r="A61" t="s">
+      <c r="A61" s="2" t="s">
         <v>187</v>
       </c>
       <c r="B61">
@@ -8900,7 +8900,7 @@
       <c r="AI61" t="s">
         <v>62</v>
       </c>
-      <c r="AJ61" s="3" t="s">
+      <c r="AJ61" s="4" t="s">
         <v>49</v>
       </c>
       <c r="AK61" t="s">
@@ -9025,7 +9025,7 @@
       <c r="AI62" t="s">
         <v>175</v>
       </c>
-      <c r="AJ62" s="2" t="s">
+      <c r="AJ62" s="3" t="s">
         <v>53</v>
       </c>
       <c r="AK62" t="s">
@@ -9150,7 +9150,7 @@
       <c r="AI63" t="s">
         <v>48</v>
       </c>
-      <c r="AJ63" s="2" t="s">
+      <c r="AJ63" s="3" t="s">
         <v>53</v>
       </c>
       <c r="AK63" t="s">
@@ -9173,7 +9173,7 @@
       </c>
     </row>
     <row r="64" spans="1:42">
-      <c r="A64" s="4" t="s">
+      <c r="A64" s="7" t="s">
         <v>191</v>
       </c>
       <c r="B64">
@@ -9233,7 +9233,7 @@
       <c r="U64">
         <v>29.44444444444445</v>
       </c>
-      <c r="V64" s="5" t="b">
+      <c r="V64" s="6" t="b">
         <v>1</v>
       </c>
       <c r="W64" t="b">
@@ -9275,7 +9275,7 @@
       <c r="AI64" t="s">
         <v>175</v>
       </c>
-      <c r="AJ64" s="3" t="s">
+      <c r="AJ64" s="4" t="s">
         <v>67</v>
       </c>
       <c r="AK64" t="s">
@@ -9400,7 +9400,7 @@
       <c r="AI65" t="s">
         <v>72</v>
       </c>
-      <c r="AJ65" s="2" t="s">
+      <c r="AJ65" s="3" t="s">
         <v>44</v>
       </c>
       <c r="AK65" t="s">
@@ -9525,7 +9525,7 @@
       <c r="AI66" t="s">
         <v>114</v>
       </c>
-      <c r="AJ66" s="2" t="s">
+      <c r="AJ66" s="3" t="s">
         <v>85</v>
       </c>
       <c r="AK66" t="s">
@@ -9650,7 +9650,7 @@
       <c r="AI67" t="s">
         <v>155</v>
       </c>
-      <c r="AJ67" s="3" t="s">
+      <c r="AJ67" s="4" t="s">
         <v>67</v>
       </c>
       <c r="AK67" t="s">
@@ -9775,7 +9775,7 @@
       <c r="AI68" t="s">
         <v>59</v>
       </c>
-      <c r="AJ68" s="2" t="s">
+      <c r="AJ68" s="3" t="s">
         <v>44</v>
       </c>
       <c r="AK68" t="s">
@@ -9897,7 +9897,7 @@
       <c r="AI69" t="s">
         <v>199</v>
       </c>
-      <c r="AJ69" s="3" t="s">
+      <c r="AJ69" s="4" t="s">
         <v>67</v>
       </c>
       <c r="AK69" t="s">
@@ -10022,7 +10022,7 @@
       <c r="AI70" t="s">
         <v>175</v>
       </c>
-      <c r="AJ70" s="3" t="s">
+      <c r="AJ70" s="4" t="s">
         <v>67</v>
       </c>
       <c r="AK70" t="s">
@@ -10072,13 +10072,13 @@
       <c r="I71">
         <v>11.09</v>
       </c>
-      <c r="J71" s="4">
+      <c r="J71" s="7">
         <v>2.8555026029693189</v>
       </c>
       <c r="K71">
         <v>11.68</v>
       </c>
-      <c r="L71" s="4">
+      <c r="L71" s="7">
         <v>3.6189281150706889</v>
       </c>
       <c r="M71">
@@ -10147,7 +10147,7 @@
       <c r="AI71" t="s">
         <v>123</v>
       </c>
-      <c r="AJ71" s="2" t="s">
+      <c r="AJ71" s="3" t="s">
         <v>85</v>
       </c>
       <c r="AK71" t="s">
@@ -10266,7 +10266,7 @@
       <c r="AI72" t="s">
         <v>116</v>
       </c>
-      <c r="AJ72" s="3" t="s">
+      <c r="AJ72" s="4" t="s">
         <v>101</v>
       </c>
       <c r="AK72" t="s">
@@ -10349,7 +10349,7 @@
       <c r="U73">
         <v>0</v>
       </c>
-      <c r="V73" s="5" t="b">
+      <c r="V73" s="6" t="b">
         <v>1</v>
       </c>
       <c r="W73" t="b">
@@ -10391,7 +10391,7 @@
       <c r="AI73" t="s">
         <v>123</v>
       </c>
-      <c r="AJ73" s="3" t="s">
+      <c r="AJ73" s="4" t="s">
         <v>49</v>
       </c>
       <c r="AK73" t="s">
@@ -10447,7 +10447,7 @@
       <c r="K74">
         <v>10.4</v>
       </c>
-      <c r="L74" s="4">
+      <c r="L74" s="7">
         <v>3.017134074665766</v>
       </c>
       <c r="M74">
@@ -10516,7 +10516,7 @@
       <c r="AI74" t="s">
         <v>84</v>
       </c>
-      <c r="AJ74" s="3" t="s">
+      <c r="AJ74" s="4" t="s">
         <v>67</v>
       </c>
       <c r="AK74" t="s">
@@ -10641,7 +10641,7 @@
       <c r="AI75" t="s">
         <v>88</v>
       </c>
-      <c r="AJ75" s="2" t="s">
+      <c r="AJ75" s="3" t="s">
         <v>85</v>
       </c>
       <c r="AK75" t="s">
@@ -10766,7 +10766,7 @@
       <c r="AI76" t="s">
         <v>56</v>
       </c>
-      <c r="AJ76" s="2" t="s">
+      <c r="AJ76" s="3" t="s">
         <v>53</v>
       </c>
       <c r="AK76" t="s">
@@ -10891,7 +10891,7 @@
       <c r="AI77" t="s">
         <v>112</v>
       </c>
-      <c r="AJ77" s="3" t="s">
+      <c r="AJ77" s="4" t="s">
         <v>49</v>
       </c>
       <c r="AK77" t="s">
@@ -10971,7 +10971,7 @@
       <c r="S78">
         <v>1.08</v>
       </c>
-      <c r="T78" s="6" t="s">
+      <c r="T78" s="8" t="s">
         <v>19</v>
       </c>
       <c r="U78">
@@ -11019,7 +11019,7 @@
       <c r="AI78" t="s">
         <v>59</v>
       </c>
-      <c r="AJ78" s="3" t="s">
+      <c r="AJ78" s="4" t="s">
         <v>67</v>
       </c>
       <c r="AK78" t="s">
@@ -11144,7 +11144,7 @@
       <c r="AI79" t="s">
         <v>43</v>
       </c>
-      <c r="AJ79" s="2" t="s">
+      <c r="AJ79" s="3" t="s">
         <v>85</v>
       </c>
       <c r="AK79" t="s">
@@ -11167,7 +11167,7 @@
       </c>
     </row>
     <row r="80" spans="1:42">
-      <c r="A80" s="4" t="s">
+      <c r="A80" s="7" t="s">
         <v>214</v>
       </c>
       <c r="B80">
@@ -11269,7 +11269,7 @@
       <c r="AI80" t="s">
         <v>56</v>
       </c>
-      <c r="AJ80" s="2" t="s">
+      <c r="AJ80" s="3" t="s">
         <v>44</v>
       </c>
       <c r="AK80" t="s">
@@ -11394,7 +11394,7 @@
       <c r="AI81" t="s">
         <v>43</v>
       </c>
-      <c r="AJ81" s="3" t="s">
+      <c r="AJ81" s="4" t="s">
         <v>101</v>
       </c>
       <c r="AK81" t="s">
@@ -11474,7 +11474,7 @@
       <c r="S82">
         <v>1.08</v>
       </c>
-      <c r="T82" s="6" t="s">
+      <c r="T82" s="8" t="s">
         <v>19</v>
       </c>
       <c r="U82">
@@ -11522,7 +11522,7 @@
       <c r="AI82" t="s">
         <v>93</v>
       </c>
-      <c r="AJ82" s="3" t="s">
+      <c r="AJ82" s="4" t="s">
         <v>49</v>
       </c>
       <c r="AK82" t="s">
@@ -11545,7 +11545,7 @@
       </c>
     </row>
     <row r="83" spans="1:42">
-      <c r="A83" s="4" t="s">
+      <c r="A83" s="7" t="s">
         <v>220</v>
       </c>
       <c r="B83">
@@ -11605,7 +11605,7 @@
       <c r="U83">
         <v>5</v>
       </c>
-      <c r="V83" s="5" t="b">
+      <c r="V83" s="6" t="b">
         <v>1</v>
       </c>
       <c r="W83" t="b">
@@ -11647,7 +11647,7 @@
       <c r="AI83" t="s">
         <v>59</v>
       </c>
-      <c r="AJ83" s="3" t="s">
+      <c r="AJ83" s="4" t="s">
         <v>67</v>
       </c>
       <c r="AK83" t="s">
@@ -11670,7 +11670,7 @@
       </c>
     </row>
     <row r="84" spans="1:42">
-      <c r="A84" s="4" t="s">
+      <c r="A84" s="7" t="s">
         <v>221</v>
       </c>
       <c r="B84">
@@ -11730,7 +11730,7 @@
       <c r="U84">
         <v>0</v>
       </c>
-      <c r="V84" s="5" t="b">
+      <c r="V84" s="6" t="b">
         <v>1</v>
       </c>
       <c r="W84" t="b">
@@ -11772,7 +11772,7 @@
       <c r="AI84" t="s">
         <v>114</v>
       </c>
-      <c r="AJ84" s="2" t="s">
+      <c r="AJ84" s="3" t="s">
         <v>89</v>
       </c>
       <c r="AK84" t="s">
@@ -11897,7 +11897,7 @@
       <c r="AI85" t="s">
         <v>43</v>
       </c>
-      <c r="AJ85" s="2" t="s">
+      <c r="AJ85" s="3" t="s">
         <v>53</v>
       </c>
       <c r="AK85" t="s">
@@ -12022,7 +12022,7 @@
       <c r="AI86" t="s">
         <v>84</v>
       </c>
-      <c r="AJ86" s="2" t="s">
+      <c r="AJ86" s="3" t="s">
         <v>44</v>
       </c>
       <c r="AK86" t="s">
@@ -12147,7 +12147,7 @@
       <c r="AI87" t="s">
         <v>59</v>
       </c>
-      <c r="AJ87" s="3" t="s">
+      <c r="AJ87" s="4" t="s">
         <v>67</v>
       </c>
       <c r="AK87" t="s">
@@ -12272,7 +12272,7 @@
       <c r="AI88" t="s">
         <v>43</v>
       </c>
-      <c r="AJ88" s="2" t="s">
+      <c r="AJ88" s="3" t="s">
         <v>85</v>
       </c>
       <c r="AK88" t="s">
@@ -12397,7 +12397,7 @@
       <c r="AI89" t="s">
         <v>73</v>
       </c>
-      <c r="AJ89" s="3" t="s">
+      <c r="AJ89" s="4" t="s">
         <v>67</v>
       </c>
       <c r="AK89" t="s">
@@ -12420,7 +12420,7 @@
       </c>
     </row>
     <row r="90" spans="1:42">
-      <c r="A90" s="4" t="s">
+      <c r="A90" s="7" t="s">
         <v>227</v>
       </c>
       <c r="B90">
@@ -12522,7 +12522,7 @@
       <c r="AI90" t="s">
         <v>84</v>
       </c>
-      <c r="AJ90" s="2" t="s">
+      <c r="AJ90" s="3" t="s">
         <v>89</v>
       </c>
       <c r="AK90" t="s">
@@ -12647,7 +12647,7 @@
       <c r="AI91" t="s">
         <v>229</v>
       </c>
-      <c r="AJ91" s="2" t="s">
+      <c r="AJ91" s="3" t="s">
         <v>53</v>
       </c>
       <c r="AK91" t="s">
@@ -12772,7 +12772,7 @@
       <c r="AI92" t="s">
         <v>84</v>
       </c>
-      <c r="AJ92" s="2" t="s">
+      <c r="AJ92" s="3" t="s">
         <v>85</v>
       </c>
       <c r="AK92" t="s">
@@ -12897,7 +12897,7 @@
       <c r="AI93" t="s">
         <v>175</v>
       </c>
-      <c r="AJ93" s="2" t="s">
+      <c r="AJ93" s="3" t="s">
         <v>53</v>
       </c>
       <c r="AK93" t="s">
@@ -13022,7 +13022,7 @@
       <c r="AI94" t="s">
         <v>73</v>
       </c>
-      <c r="AJ94" s="2" t="s">
+      <c r="AJ94" s="3" t="s">
         <v>53</v>
       </c>
       <c r="AK94" t="s">
@@ -13072,13 +13072,13 @@
       <c r="I95">
         <v>25.62</v>
       </c>
-      <c r="J95" s="4">
+      <c r="J95" s="7">
         <v>8.0339311699048963</v>
       </c>
       <c r="K95">
         <v>15.37</v>
       </c>
-      <c r="L95" s="4">
+      <c r="L95" s="7">
         <v>5.3537874971755057</v>
       </c>
       <c r="M95">
@@ -13147,7 +13147,7 @@
       <c r="AI95" t="s">
         <v>116</v>
       </c>
-      <c r="AJ95" s="2" t="s">
+      <c r="AJ95" s="3" t="s">
         <v>85</v>
       </c>
       <c r="AK95" t="s">
@@ -13272,7 +13272,7 @@
       <c r="AI96" t="s">
         <v>84</v>
       </c>
-      <c r="AJ96" s="2" t="s">
+      <c r="AJ96" s="3" t="s">
         <v>156</v>
       </c>
       <c r="AK96" t="s">
@@ -13295,7 +13295,7 @@
       </c>
     </row>
     <row r="97" spans="1:42">
-      <c r="A97" s="4" t="s">
+      <c r="A97" s="7" t="s">
         <v>239</v>
       </c>
       <c r="B97">
@@ -13355,7 +13355,7 @@
       <c r="U97">
         <v>0</v>
       </c>
-      <c r="V97" s="5" t="b">
+      <c r="V97" s="6" t="b">
         <v>1</v>
       </c>
       <c r="W97" t="b">
@@ -13397,7 +13397,7 @@
       <c r="AI97" t="s">
         <v>56</v>
       </c>
-      <c r="AJ97" s="2" t="s">
+      <c r="AJ97" s="3" t="s">
         <v>89</v>
       </c>
       <c r="AK97" t="s">
@@ -13522,7 +13522,7 @@
       <c r="AI98" t="s">
         <v>48</v>
       </c>
-      <c r="AJ98" s="2" t="s">
+      <c r="AJ98" s="3" t="s">
         <v>53</v>
       </c>
       <c r="AK98" t="s">
@@ -13545,7 +13545,7 @@
       </c>
     </row>
     <row r="99" spans="1:42">
-      <c r="A99" s="4" t="s">
+      <c r="A99" s="7" t="s">
         <v>242</v>
       </c>
       <c r="B99">
@@ -13650,7 +13650,7 @@
       <c r="AI99" t="s">
         <v>93</v>
       </c>
-      <c r="AJ99" s="3" t="s">
+      <c r="AJ99" s="4" t="s">
         <v>67</v>
       </c>
       <c r="AK99" t="s">
@@ -13700,7 +13700,7 @@
       <c r="I100">
         <v>11.64</v>
       </c>
-      <c r="J100" s="4">
+      <c r="J100" s="7">
         <v>3.051520201855388</v>
       </c>
       <c r="K100">
@@ -13775,7 +13775,7 @@
       <c r="AI100" t="s">
         <v>66</v>
       </c>
-      <c r="AJ100" s="2" t="s">
+      <c r="AJ100" s="3" t="s">
         <v>53</v>
       </c>
       <c r="AK100" t="s">
@@ -13858,7 +13858,7 @@
       <c r="U101">
         <v>0</v>
       </c>
-      <c r="V101" s="5" t="b">
+      <c r="V101" s="6" t="b">
         <v>1</v>
       </c>
       <c r="W101" t="b">
@@ -13900,7 +13900,7 @@
       <c r="AI101" t="s">
         <v>93</v>
       </c>
-      <c r="AJ101" s="2" t="s">
+      <c r="AJ101" s="3" t="s">
         <v>156</v>
       </c>
       <c r="AK101" t="s">
@@ -14025,7 +14025,7 @@
       <c r="AI102" t="s">
         <v>43</v>
       </c>
-      <c r="AJ102" s="2" t="s">
+      <c r="AJ102" s="3" t="s">
         <v>53</v>
       </c>
       <c r="AK102" t="s">
@@ -14108,7 +14108,7 @@
       <c r="U103">
         <v>6.1111111111111107</v>
       </c>
-      <c r="V103" s="5" t="b">
+      <c r="V103" s="6" t="b">
         <v>1</v>
       </c>
       <c r="W103" t="b">
@@ -14150,7 +14150,7 @@
       <c r="AI103" t="s">
         <v>48</v>
       </c>
-      <c r="AJ103" s="2" t="s">
+      <c r="AJ103" s="3" t="s">
         <v>156</v>
       </c>
       <c r="AK103" t="s">
@@ -14275,7 +14275,7 @@
       <c r="AI104" t="s">
         <v>175</v>
       </c>
-      <c r="AJ104" s="2" t="s">
+      <c r="AJ104" s="3" t="s">
         <v>53</v>
       </c>
       <c r="AK104" t="s">
@@ -14400,7 +14400,7 @@
       <c r="AI105" t="s">
         <v>93</v>
       </c>
-      <c r="AJ105" s="3" t="s">
+      <c r="AJ105" s="4" t="s">
         <v>67</v>
       </c>
       <c r="AK105" t="s">
@@ -14525,7 +14525,7 @@
       <c r="AI106" t="s">
         <v>116</v>
       </c>
-      <c r="AJ106" s="3" t="s">
+      <c r="AJ106" s="4" t="s">
         <v>101</v>
       </c>
       <c r="AK106" t="s">
@@ -14650,7 +14650,7 @@
       <c r="AI107" t="s">
         <v>253</v>
       </c>
-      <c r="AJ107" s="3" t="s">
+      <c r="AJ107" s="4" t="s">
         <v>101</v>
       </c>
       <c r="AK107" t="s">
@@ -14772,7 +14772,7 @@
       <c r="AI108" t="s">
         <v>93</v>
       </c>
-      <c r="AJ108" s="3" t="s">
+      <c r="AJ108" s="4" t="s">
         <v>49</v>
       </c>
       <c r="AK108" t="s">
@@ -14894,7 +14894,7 @@
       <c r="AI109" t="s">
         <v>93</v>
       </c>
-      <c r="AJ109" s="2" t="s">
+      <c r="AJ109" s="3" t="s">
         <v>44</v>
       </c>
       <c r="AK109" t="s">
@@ -15019,7 +15019,7 @@
       <c r="AI110" t="s">
         <v>81</v>
       </c>
-      <c r="AJ110" s="3" t="s">
+      <c r="AJ110" s="4" t="s">
         <v>101</v>
       </c>
       <c r="AK110" t="s">
@@ -15144,7 +15144,7 @@
       <c r="AI111" t="s">
         <v>93</v>
       </c>
-      <c r="AJ111" s="2" t="s">
+      <c r="AJ111" s="3" t="s">
         <v>53</v>
       </c>
       <c r="AK111" t="s">
@@ -15269,7 +15269,7 @@
       <c r="AI112" t="s">
         <v>93</v>
       </c>
-      <c r="AJ112" s="3" t="s">
+      <c r="AJ112" s="4" t="s">
         <v>67</v>
       </c>
       <c r="AK112" t="s">
@@ -15394,7 +15394,7 @@
       <c r="AI113" t="s">
         <v>84</v>
       </c>
-      <c r="AJ113" s="2" t="s">
+      <c r="AJ113" s="3" t="s">
         <v>53</v>
       </c>
       <c r="AK113" t="s">
@@ -15519,7 +15519,7 @@
       <c r="AI114" t="s">
         <v>56</v>
       </c>
-      <c r="AJ114" s="2" t="s">
+      <c r="AJ114" s="3" t="s">
         <v>53</v>
       </c>
       <c r="AK114" t="s">
@@ -15644,7 +15644,7 @@
       <c r="AI115" t="s">
         <v>48</v>
       </c>
-      <c r="AJ115" s="2" t="s">
+      <c r="AJ115" s="3" t="s">
         <v>85</v>
       </c>
       <c r="AK115" t="s">
@@ -15667,7 +15667,7 @@
       </c>
     </row>
     <row r="116" spans="1:42">
-      <c r="A116" s="4" t="s">
+      <c r="A116" s="7" t="s">
         <v>264</v>
       </c>
       <c r="B116">
@@ -15769,7 +15769,7 @@
       <c r="AI116" t="s">
         <v>93</v>
       </c>
-      <c r="AJ116" s="2" t="s">
+      <c r="AJ116" s="3" t="s">
         <v>85</v>
       </c>
       <c r="AK116" t="s">
@@ -15792,7 +15792,7 @@
       </c>
     </row>
     <row r="117" spans="1:42">
-      <c r="A117" s="4" t="s">
+      <c r="A117" s="7" t="s">
         <v>265</v>
       </c>
       <c r="B117">
@@ -15894,7 +15894,7 @@
       <c r="AI117" t="s">
         <v>112</v>
       </c>
-      <c r="AJ117" s="3" t="s">
+      <c r="AJ117" s="4" t="s">
         <v>266</v>
       </c>
       <c r="AK117" t="s">
@@ -15977,7 +15977,7 @@
       <c r="U118">
         <v>5</v>
       </c>
-      <c r="V118" s="5" t="b">
+      <c r="V118" s="6" t="b">
         <v>1</v>
       </c>
       <c r="W118" t="b">
@@ -16019,7 +16019,7 @@
       <c r="AI118" t="s">
         <v>93</v>
       </c>
-      <c r="AJ118" s="2" t="s">
+      <c r="AJ118" s="3" t="s">
         <v>53</v>
       </c>
       <c r="AK118" t="s">
@@ -16042,7 +16042,7 @@
       </c>
     </row>
     <row r="119" spans="1:42">
-      <c r="A119" t="s">
+      <c r="A119" s="2" t="s">
         <v>270</v>
       </c>
       <c r="B119">
@@ -16144,7 +16144,7 @@
       <c r="AI119" t="s">
         <v>56</v>
       </c>
-      <c r="AJ119" s="3" t="s">
+      <c r="AJ119" s="4" t="s">
         <v>67</v>
       </c>
       <c r="AK119" t="s">
@@ -16269,7 +16269,7 @@
       <c r="AI120" t="s">
         <v>93</v>
       </c>
-      <c r="AJ120" s="2" t="s">
+      <c r="AJ120" s="3" t="s">
         <v>53</v>
       </c>
       <c r="AK120" t="s">
@@ -16394,7 +16394,7 @@
       <c r="AI121" t="s">
         <v>114</v>
       </c>
-      <c r="AJ121" s="3" t="s">
+      <c r="AJ121" s="4" t="s">
         <v>101</v>
       </c>
       <c r="AK121" t="s">
@@ -16444,13 +16444,13 @@
       <c r="I122">
         <v>10.1</v>
       </c>
-      <c r="J122" s="4">
+      <c r="J122" s="7">
         <v>2.5026709249743968</v>
       </c>
       <c r="K122">
         <v>11.59</v>
       </c>
-      <c r="L122" s="4">
+      <c r="L122" s="7">
         <v>3.5766144716047181</v>
       </c>
       <c r="M122">
@@ -16519,7 +16519,7 @@
       <c r="AI122" t="s">
         <v>116</v>
       </c>
-      <c r="AJ122" s="2" t="s">
+      <c r="AJ122" s="3" t="s">
         <v>89</v>
       </c>
       <c r="AK122" t="s">
@@ -16602,7 +16602,7 @@
       <c r="U123">
         <v>1.666666666666667</v>
       </c>
-      <c r="V123" s="5" t="b">
+      <c r="V123" s="6" t="b">
         <v>1</v>
       </c>
       <c r="W123" t="b">
@@ -16644,7 +16644,7 @@
       <c r="AI123" t="s">
         <v>43</v>
       </c>
-      <c r="AJ123" s="2" t="s">
+      <c r="AJ123" s="3" t="s">
         <v>85</v>
       </c>
       <c r="AK123" t="s">
@@ -16667,7 +16667,7 @@
       </c>
     </row>
     <row r="124" spans="1:42">
-      <c r="A124" s="4" t="s">
+      <c r="A124" s="7" t="s">
         <v>277</v>
       </c>
       <c r="B124">
@@ -16769,7 +16769,7 @@
       <c r="AI124" t="s">
         <v>278</v>
       </c>
-      <c r="AJ124" s="3" t="s">
+      <c r="AJ124" s="4" t="s">
         <v>67</v>
       </c>
       <c r="AK124" t="s">
@@ -16894,7 +16894,7 @@
       <c r="AI125" t="s">
         <v>84</v>
       </c>
-      <c r="AJ125" s="3" t="s">
+      <c r="AJ125" s="4" t="s">
         <v>101</v>
       </c>
       <c r="AK125" t="s">
@@ -17019,7 +17019,7 @@
       <c r="AI126" t="s">
         <v>52</v>
       </c>
-      <c r="AJ126" s="3" t="s">
+      <c r="AJ126" s="4" t="s">
         <v>101</v>
       </c>
       <c r="AK126" t="s">
@@ -17042,7 +17042,7 @@
       </c>
     </row>
     <row r="127" spans="1:42">
-      <c r="A127" t="s">
+      <c r="A127" s="2" t="s">
         <v>281</v>
       </c>
       <c r="B127">
@@ -17099,7 +17099,7 @@
       <c r="S127">
         <v>1.48</v>
       </c>
-      <c r="T127" s="6" t="s">
+      <c r="T127" s="8" t="s">
         <v>19</v>
       </c>
       <c r="U127">
@@ -17147,7 +17147,7 @@
       <c r="AI127" t="s">
         <v>93</v>
       </c>
-      <c r="AJ127" s="3" t="s">
+      <c r="AJ127" s="4" t="s">
         <v>67</v>
       </c>
       <c r="AK127" t="s">
@@ -17272,7 +17272,7 @@
       <c r="AI128" t="s">
         <v>59</v>
       </c>
-      <c r="AJ128" s="2" t="s">
+      <c r="AJ128" s="3" t="s">
         <v>89</v>
       </c>
       <c r="AK128" t="s">
@@ -17397,7 +17397,7 @@
       <c r="AI129" t="s">
         <v>48</v>
       </c>
-      <c r="AJ129" s="3" t="s">
+      <c r="AJ129" s="4" t="s">
         <v>49</v>
       </c>
       <c r="AK129" t="s">
@@ -17519,7 +17519,7 @@
       <c r="AI130" t="s">
         <v>116</v>
       </c>
-      <c r="AJ130" s="3" t="s">
+      <c r="AJ130" s="4" t="s">
         <v>67</v>
       </c>
       <c r="AK130" t="s">
@@ -17542,7 +17542,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>